--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37D8AE0-69A6-43DD-AEF4-BD853A445F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F77F7F-1E3B-4F78-B065-EDB3A37D243F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="410">
   <si>
     <t>id</t>
   </si>
@@ -867,9 +867,6 @@
     <t>cuidados paliativos y alivio del dolor</t>
   </si>
   <si>
-    <t>josé molina alavarez</t>
-  </si>
-  <si>
     <t>cuidados hematooncológico hospitalizado</t>
   </si>
   <si>
@@ -879,9 +876,6 @@
     <t>evelyn.salinas@redsalud.gob.cl</t>
   </si>
   <si>
-    <t>coordinación hematooncológica</t>
-  </si>
-  <si>
     <t>cuidados hospitalización domiciliaria</t>
   </si>
   <si>
@@ -1174,13 +1168,112 @@
   </si>
   <si>
     <t>desarrollo estratégico</t>
+  </si>
+  <si>
+    <t>imagenología</t>
+  </si>
+  <si>
+    <t>patricia guzmán falcón</t>
+  </si>
+  <si>
+    <t>patricia.guzman.f@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>marcela fuentes tapia</t>
+  </si>
+  <si>
+    <t>marcela.fuentest@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>banco de sangre</t>
+  </si>
+  <si>
+    <t>claudia molina garcía</t>
+  </si>
+  <si>
+    <t>claudia.molinag@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>francia gonzález castillo</t>
+  </si>
+  <si>
+    <t>francia.gonzalez@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>anatomía patológica</t>
+  </si>
+  <si>
+    <t>andrés rodríguez schneider</t>
+  </si>
+  <si>
+    <t>andres.rodriguez.s@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>marcelo lara delgado</t>
+  </si>
+  <si>
+    <t>marcelo.lara@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>medicina nuclear</t>
+  </si>
+  <si>
+    <t>gilda donoso rosello</t>
+  </si>
+  <si>
+    <t>gilda.donoso@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>niusta vega</t>
+  </si>
+  <si>
+    <t>niusta.vega@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>laboratorio clínico</t>
+  </si>
+  <si>
+    <t>andrea amaro espinoza</t>
+  </si>
+  <si>
+    <t>andrea.amaro@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>mónica soto solís</t>
+  </si>
+  <si>
+    <t>monica.soto@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>farmacia</t>
+  </si>
+  <si>
+    <t>eliana pizarro ibarra</t>
+  </si>
+  <si>
+    <t>eliana.pizarro@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>luciano carimán castillo</t>
+  </si>
+  <si>
+    <t>luciano.cariman@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>apoyo clínico</t>
+  </si>
+  <si>
+    <t>jeanette.lillob@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>josé molina álvarez</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1215,12 +1308,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1555,24 +1649,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
-  <dimension ref="A1:H151"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <dimension ref="A1:H150"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C1" t="s">
         <v>168</v>
@@ -1593,7 +1687,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1616,7 +1710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1639,7 +1733,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1662,7 +1756,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1685,7 +1779,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1708,7 +1802,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1731,7 +1825,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1754,7 +1848,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1777,7 +1871,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1800,7 +1894,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1823,7 +1917,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1846,7 +1940,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1869,7 +1963,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1892,7 +1986,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1915,7 +2009,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1938,7 +2032,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1961,7 +2055,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1984,7 +2078,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2007,7 +2101,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2030,7 +2124,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2053,7 +2147,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2076,7 +2170,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2099,7 +2193,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2122,7 +2216,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2145,7 +2239,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2168,7 +2262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2191,7 +2285,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2214,7 +2308,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2225,10 +2319,10 @@
         <v>145</v>
       </c>
       <c r="D29" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E29" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F29" t="s">
         <v>44</v>
@@ -2237,7 +2331,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2260,7 +2354,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2283,7 +2377,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2306,7 +2400,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2329,7 +2423,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2352,7 +2446,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2375,7 +2469,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2398,7 +2492,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2421,7 +2515,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2444,7 +2538,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2467,7 +2561,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2490,7 +2584,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2513,7 +2607,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2536,7 +2630,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2559,7 +2653,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2573,7 +2667,7 @@
         <v>195</v>
       </c>
       <c r="E44" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>82</v>
@@ -2582,7 +2676,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2596,7 +2690,7 @@
         <v>197</v>
       </c>
       <c r="E45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>82</v>
@@ -2605,7 +2699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2628,7 +2722,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2642,7 +2736,7 @@
         <v>202</v>
       </c>
       <c r="E47" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>82</v>
@@ -2651,7 +2745,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2664,8 +2758,8 @@
       <c r="D48" t="s">
         <v>204</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>82</v>
+      <c r="E48" s="3" t="s">
+        <v>408</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>82</v>
@@ -2674,7 +2768,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2688,7 +2782,7 @@
         <v>206</v>
       </c>
       <c r="E49" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>82</v>
@@ -2697,7 +2791,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2720,7 +2814,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2734,7 +2828,7 @@
         <v>211</v>
       </c>
       <c r="E51" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>82</v>
@@ -2743,7 +2837,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2757,7 +2851,7 @@
         <v>213</v>
       </c>
       <c r="E52" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>82</v>
@@ -2766,7 +2860,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2780,7 +2874,7 @@
         <v>215</v>
       </c>
       <c r="E53" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>82</v>
@@ -2789,7 +2883,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2803,7 +2897,7 @@
         <v>217</v>
       </c>
       <c r="E54" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>82</v>
@@ -2812,7 +2906,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2835,7 +2929,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2849,7 +2943,7 @@
         <v>222</v>
       </c>
       <c r="E56" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>82</v>
@@ -2858,7 +2952,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2872,7 +2966,7 @@
         <v>224</v>
       </c>
       <c r="E57" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>82</v>
@@ -2881,7 +2975,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2895,7 +2989,7 @@
         <v>226</v>
       </c>
       <c r="E58" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>82</v>
@@ -2904,7 +2998,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2927,7 +3021,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2950,7 +3044,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2964,7 +3058,7 @@
         <v>234</v>
       </c>
       <c r="E61" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>82</v>
@@ -2973,7 +3067,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2996,7 +3090,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3019,7 +3113,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3033,7 +3127,7 @@
         <v>242</v>
       </c>
       <c r="E64" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>82</v>
@@ -3042,7 +3136,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3056,7 +3150,7 @@
         <v>244</v>
       </c>
       <c r="E65" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>82</v>
@@ -3065,7 +3159,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3088,7 +3182,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3102,7 +3196,7 @@
         <v>249</v>
       </c>
       <c r="E67" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>82</v>
@@ -3111,7 +3205,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3134,7 +3228,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3148,7 +3242,7 @@
         <v>254</v>
       </c>
       <c r="E69" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>82</v>
@@ -3157,7 +3251,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
@@ -3180,7 +3274,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
@@ -3194,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="E71" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>82</v>
@@ -3203,7 +3297,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
@@ -3217,7 +3311,7 @@
         <v>261</v>
       </c>
       <c r="E72" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>82</v>
@@ -3226,7 +3320,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>72</v>
       </c>
@@ -3249,7 +3343,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>73</v>
       </c>
@@ -3263,7 +3357,7 @@
         <v>266</v>
       </c>
       <c r="E74" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>82</v>
@@ -3272,7 +3366,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>74</v>
       </c>
@@ -3295,7 +3389,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>75</v>
       </c>
@@ -3318,7 +3412,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>76</v>
       </c>
@@ -3341,7 +3435,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>77</v>
       </c>
@@ -3352,7 +3446,7 @@
         <v>275</v>
       </c>
       <c r="D78" t="s">
-        <v>276</v>
+        <v>409</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>82</v>
@@ -3364,7 +3458,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>78</v>
       </c>
@@ -3372,36 +3466,36 @@
         <v>193</v>
       </c>
       <c r="C79" t="s">
+        <v>276</v>
+      </c>
+      <c r="D79" t="s">
         <v>277</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>278</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>80</v>
+      </c>
+      <c r="B80" t="s">
+        <v>193</v>
+      </c>
+      <c r="C80" t="s">
         <v>279</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="s">
-        <v>193</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>280</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>82</v>
+      <c r="E80" t="s">
+        <v>323</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>82</v>
@@ -3410,9 +3504,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" t="s">
         <v>193</v>
@@ -3424,7 +3518,7 @@
         <v>282</v>
       </c>
       <c r="E81" t="s">
-        <v>325</v>
+        <v>283</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>82</v>
@@ -3433,21 +3527,21 @@
         <v>82</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" t="s">
         <v>193</v>
       </c>
       <c r="C82" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D82" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E82" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>82</v>
@@ -3456,21 +3550,21 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" t="s">
         <v>193</v>
       </c>
       <c r="C83" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D83" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E83" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>82</v>
@@ -3479,21 +3573,21 @@
         <v>82</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" t="s">
         <v>193</v>
       </c>
       <c r="C84" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D84" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E84" t="s">
-        <v>291</v>
+        <v>324</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>82</v>
@@ -3502,9 +3596,9 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
         <v>193</v>
@@ -3516,629 +3610,714 @@
         <v>293</v>
       </c>
       <c r="E85" t="s">
+        <v>294</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>86</v>
+      </c>
+      <c r="B86" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" t="s">
+        <v>295</v>
+      </c>
+      <c r="D86" t="s">
+        <v>296</v>
+      </c>
+      <c r="E86" t="s">
+        <v>297</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>87</v>
+      </c>
+      <c r="B87" t="s">
+        <v>193</v>
+      </c>
+      <c r="C87" t="s">
+        <v>298</v>
+      </c>
+      <c r="D87" t="s">
+        <v>299</v>
+      </c>
+      <c r="E87" t="s">
+        <v>300</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>88</v>
+      </c>
+      <c r="B88" t="s">
+        <v>193</v>
+      </c>
+      <c r="C88" t="s">
+        <v>301</v>
+      </c>
+      <c r="D88" t="s">
+        <v>302</v>
+      </c>
+      <c r="E88" t="s">
+        <v>303</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
         <v>326</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="s">
-        <v>193</v>
-      </c>
-      <c r="C86" t="s">
-        <v>294</v>
-      </c>
-      <c r="D86" t="s">
-        <v>295</v>
-      </c>
-      <c r="E86" t="s">
-        <v>296</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7">
-      <c r="A87">
-        <v>86</v>
-      </c>
-      <c r="B87" t="s">
-        <v>193</v>
-      </c>
-      <c r="C87" t="s">
-        <v>297</v>
-      </c>
-      <c r="D87" t="s">
-        <v>298</v>
-      </c>
-      <c r="E87" t="s">
-        <v>299</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
-      <c r="A88">
-        <v>87</v>
-      </c>
-      <c r="B88" t="s">
-        <v>193</v>
-      </c>
-      <c r="C88" t="s">
-        <v>300</v>
-      </c>
-      <c r="D88" t="s">
-        <v>301</v>
-      </c>
-      <c r="E88" t="s">
-        <v>302</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
-      <c r="A89">
-        <v>88</v>
-      </c>
-      <c r="B89" t="s">
-        <v>193</v>
-      </c>
-      <c r="C89" t="s">
-        <v>303</v>
-      </c>
-      <c r="D89" t="s">
-        <v>304</v>
+      <c r="C89" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>328</v>
       </c>
       <c r="E89" t="s">
-        <v>305</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+        <v>329</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="G89" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E90" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G90" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E91" t="s">
+        <v>339</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="E91" t="s">
+      <c r="G91" t="s">
         <v>336</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="G91" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E92" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="G92" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E93" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="G93" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E94" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G94" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" t="s">
-        <v>328</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>351</v>
+        <v>376</v>
+      </c>
+      <c r="C95" t="s">
+        <v>355</v>
+      </c>
+      <c r="D95" t="s">
+        <v>356</v>
       </c>
       <c r="E95" t="s">
-        <v>352</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
+      </c>
+      <c r="F95" t="s">
+        <v>358</v>
       </c>
       <c r="G95" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" t="s">
+        <v>376</v>
+      </c>
+      <c r="C96" t="s">
+        <v>360</v>
+      </c>
+      <c r="D96" t="s">
+        <v>361</v>
+      </c>
+      <c r="E96" t="s">
+        <v>362</v>
+      </c>
+      <c r="F96" t="s">
+        <v>44</v>
+      </c>
+      <c r="G96" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>97</v>
+      </c>
+      <c r="B97" t="s">
+        <v>376</v>
+      </c>
+      <c r="C97" t="s">
+        <v>363</v>
+      </c>
+      <c r="D97" t="s">
+        <v>364</v>
+      </c>
+      <c r="E97" t="s">
+        <v>365</v>
+      </c>
+      <c r="F97" t="s">
+        <v>366</v>
+      </c>
+      <c r="G97" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>376</v>
+      </c>
+      <c r="C98" t="s">
+        <v>368</v>
+      </c>
+      <c r="D98" t="s">
+        <v>369</v>
+      </c>
+      <c r="E98" t="s">
+        <v>370</v>
+      </c>
+      <c r="F98" t="s">
+        <v>371</v>
+      </c>
+      <c r="G98" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>99</v>
+      </c>
+      <c r="B99" t="s">
+        <v>376</v>
+      </c>
+      <c r="C99" t="s">
+        <v>373</v>
+      </c>
+      <c r="D99" t="s">
+        <v>374</v>
+      </c>
+      <c r="E99" t="s">
+        <v>375</v>
+      </c>
+      <c r="F99" t="s">
+        <v>44</v>
+      </c>
+      <c r="G99" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>100</v>
+      </c>
+      <c r="B100" t="s">
+        <v>407</v>
+      </c>
+      <c r="C100" t="s">
+        <v>377</v>
+      </c>
+      <c r="D100" t="s">
         <v>378</v>
       </c>
-      <c r="C96" t="s">
-        <v>357</v>
-      </c>
-      <c r="D96" t="s">
-        <v>358</v>
-      </c>
-      <c r="E96" t="s">
-        <v>359</v>
-      </c>
-      <c r="F96" t="s">
-        <v>360</v>
-      </c>
-      <c r="G96" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7">
-      <c r="A97">
-        <v>96</v>
-      </c>
-      <c r="B97" t="s">
-        <v>378</v>
-      </c>
-      <c r="C97" t="s">
-        <v>362</v>
-      </c>
-      <c r="D97" t="s">
-        <v>363</v>
-      </c>
-      <c r="E97" t="s">
-        <v>364</v>
-      </c>
-      <c r="F97" t="s">
-        <v>44</v>
-      </c>
-      <c r="G97" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7">
-      <c r="A98">
-        <v>97</v>
-      </c>
-      <c r="B98" t="s">
-        <v>378</v>
-      </c>
-      <c r="C98" t="s">
-        <v>365</v>
-      </c>
-      <c r="D98" t="s">
-        <v>366</v>
-      </c>
-      <c r="E98" t="s">
-        <v>367</v>
-      </c>
-      <c r="F98" t="s">
-        <v>368</v>
-      </c>
-      <c r="G98" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7">
-      <c r="A99">
-        <v>98</v>
-      </c>
-      <c r="B99" t="s">
-        <v>378</v>
-      </c>
-      <c r="C99" t="s">
-        <v>370</v>
-      </c>
-      <c r="D99" t="s">
-        <v>371</v>
-      </c>
-      <c r="E99" t="s">
-        <v>372</v>
-      </c>
-      <c r="F99" t="s">
-        <v>373</v>
-      </c>
-      <c r="G99" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7">
-      <c r="A100">
-        <v>99</v>
-      </c>
-      <c r="B100" t="s">
-        <v>378</v>
-      </c>
-      <c r="C100" t="s">
-        <v>375</v>
-      </c>
-      <c r="D100" t="s">
-        <v>376</v>
-      </c>
       <c r="E100" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F100" t="s">
-        <v>44</v>
+        <v>380</v>
       </c>
       <c r="G100" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7">
+        <v>101</v>
+      </c>
+      <c r="B101" t="s">
+        <v>407</v>
+      </c>
+      <c r="C101" t="s">
+        <v>382</v>
+      </c>
+      <c r="D101" t="s">
+        <v>383</v>
+      </c>
+      <c r="E101" t="s">
+        <v>384</v>
+      </c>
+      <c r="F101" t="s">
+        <v>385</v>
+      </c>
+      <c r="G101" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7">
+        <v>102</v>
+      </c>
+      <c r="B102" t="s">
+        <v>407</v>
+      </c>
+      <c r="C102" t="s">
+        <v>387</v>
+      </c>
+      <c r="D102" t="s">
+        <v>388</v>
+      </c>
+      <c r="E102" t="s">
+        <v>389</v>
+      </c>
+      <c r="F102" t="s">
+        <v>390</v>
+      </c>
+      <c r="G102" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7">
+        <v>103</v>
+      </c>
+      <c r="B103" t="s">
+        <v>407</v>
+      </c>
+      <c r="C103" t="s">
+        <v>392</v>
+      </c>
+      <c r="D103" t="s">
+        <v>393</v>
+      </c>
+      <c r="E103" t="s">
+        <v>394</v>
+      </c>
+      <c r="F103" t="s">
+        <v>395</v>
+      </c>
+      <c r="G103" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7">
+        <v>104</v>
+      </c>
+      <c r="B104" t="s">
+        <v>407</v>
+      </c>
+      <c r="C104" t="s">
+        <v>397</v>
+      </c>
+      <c r="D104" t="s">
+        <v>398</v>
+      </c>
+      <c r="E104" t="s">
+        <v>399</v>
+      </c>
+      <c r="F104" t="s">
+        <v>400</v>
+      </c>
+      <c r="G104" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7">
+        <v>105</v>
+      </c>
+      <c r="B105" t="s">
+        <v>407</v>
+      </c>
+      <c r="C105" t="s">
+        <v>402</v>
+      </c>
+      <c r="D105" t="s">
+        <v>403</v>
+      </c>
+      <c r="E105" t="s">
+        <v>404</v>
+      </c>
+      <c r="F105" t="s">
+        <v>405</v>
+      </c>
+      <c r="G105" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E90" r:id="rId1" display="mailto:miriam.sotov@redsalud.gob.cl" xr:uid="{CA864F29-52B2-43C7-A13E-76AEC8A49A4F}"/>
-    <hyperlink ref="G90" r:id="rId2" display="mailto:sandra.felipe@redsalud.gob.cl" xr:uid="{E976CC02-5359-4441-A979-BD71659626F9}"/>
-    <hyperlink ref="E91" r:id="rId3" display="mailto:mariela.gallardo@redsalud.gob.cl" xr:uid="{9C732FB4-A61F-4E39-B898-750F2EC775F1}"/>
-    <hyperlink ref="G91" r:id="rId4" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{C4E3479B-2B05-4DD8-8E11-9D8BF2B85E31}"/>
-    <hyperlink ref="E92" r:id="rId5" display="mailto:valentina.molinah@redsalud.gob.cl" xr:uid="{C1ADBA44-5B7A-4977-AABE-11063BE1B6A7}"/>
-    <hyperlink ref="G92" r:id="rId6" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{D04DDA16-E51A-4689-BBD7-423B1C3B374F}"/>
-    <hyperlink ref="E93" r:id="rId7" display="mailto:ariel.davila.q@redsalud.gob.cl" xr:uid="{EC233077-E60B-496D-AE88-C023286395AA}"/>
-    <hyperlink ref="G93" r:id="rId8" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{83E83D38-31B5-4021-9A85-A21840781BD6}"/>
-    <hyperlink ref="E94" r:id="rId9" display="mailto:veronica.perez.gutierrez@redsalud.gob.cl" xr:uid="{FA6F0642-EBF9-4CD6-9C47-58B1F0F3E6C0}"/>
-    <hyperlink ref="G94" r:id="rId10" display="mailto:adriana.toledo@redsalud.gob.cl" xr:uid="{CD766FCC-3306-4798-96D5-1B84D28ECDC6}"/>
-    <hyperlink ref="E95" r:id="rId11" display="mailto:romy.geissbuhler@redsalud.gob.cl" xr:uid="{7D4D5B0A-0E35-49DA-AA2E-78A73F7C081E}"/>
-    <hyperlink ref="G95" r:id="rId12" display="mailto:marisol.lara@redsalud.gob.cl" xr:uid="{49F93AE7-78F6-409A-802B-D4EFCB8ABFD3}"/>
+    <hyperlink ref="E89" r:id="rId1" display="mailto:miriam.sotov@redsalud.gob.cl" xr:uid="{CA864F29-52B2-43C7-A13E-76AEC8A49A4F}"/>
+    <hyperlink ref="G89" r:id="rId2" display="mailto:sandra.felipe@redsalud.gob.cl" xr:uid="{E976CC02-5359-4441-A979-BD71659626F9}"/>
+    <hyperlink ref="E90" r:id="rId3" display="mailto:mariela.gallardo@redsalud.gob.cl" xr:uid="{9C732FB4-A61F-4E39-B898-750F2EC775F1}"/>
+    <hyperlink ref="G90" r:id="rId4" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{C4E3479B-2B05-4DD8-8E11-9D8BF2B85E31}"/>
+    <hyperlink ref="E91" r:id="rId5" display="mailto:valentina.molinah@redsalud.gob.cl" xr:uid="{C1ADBA44-5B7A-4977-AABE-11063BE1B6A7}"/>
+    <hyperlink ref="G91" r:id="rId6" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{D04DDA16-E51A-4689-BBD7-423B1C3B374F}"/>
+    <hyperlink ref="E92" r:id="rId7" display="mailto:ariel.davila.q@redsalud.gob.cl" xr:uid="{EC233077-E60B-496D-AE88-C023286395AA}"/>
+    <hyperlink ref="G92" r:id="rId8" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{83E83D38-31B5-4021-9A85-A21840781BD6}"/>
+    <hyperlink ref="E93" r:id="rId9" display="mailto:veronica.perez.gutierrez@redsalud.gob.cl" xr:uid="{FA6F0642-EBF9-4CD6-9C47-58B1F0F3E6C0}"/>
+    <hyperlink ref="G93" r:id="rId10" display="mailto:adriana.toledo@redsalud.gob.cl" xr:uid="{CD766FCC-3306-4798-96D5-1B84D28ECDC6}"/>
+    <hyperlink ref="E94" r:id="rId11" display="mailto:romy.geissbuhler@redsalud.gob.cl" xr:uid="{7D4D5B0A-0E35-49DA-AA2E-78A73F7C081E}"/>
+    <hyperlink ref="G94" r:id="rId12" display="mailto:marisol.lara@redsalud.gob.cl" xr:uid="{49F93AE7-78F6-409A-802B-D4EFCB8ABFD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F77F7F-1E3B-4F78-B065-EDB3A37D243F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FCB9C4-B7EF-4B34-80F4-B134BB523657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="427">
   <si>
     <t>id</t>
   </si>
@@ -1267,6 +1267,57 @@
   </si>
   <si>
     <t>josé molina álvarez</t>
+  </si>
+  <si>
+    <t>gineco obstetricia</t>
+  </si>
+  <si>
+    <t>cynthia.ibarra@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jasmina.campos@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>barbara.padilla@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>cecilia.diaz@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>juan.clark@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>francisca.gomez.f@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>camila.figueroa.v@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jasmina jeannette campos lucero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cecilia nathalie díaz osorio </t>
+  </si>
+  <si>
+    <t xml:space="preserve">maría isabel ortiz guerrero </t>
+  </si>
+  <si>
+    <t>jessica pino apiolaza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cynthia roxana ibarra armijo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">barbara pia padilla gonzález </t>
+  </si>
+  <si>
+    <t xml:space="preserve">juan matías clark gonzález </t>
+  </si>
+  <si>
+    <t xml:space="preserve">francisca javiera gómez fuentes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">camila catalina figueroa villagra </t>
   </si>
 </sst>
 </file>
@@ -1308,13 +1359,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1649,7 +1699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -2566,22 +2616,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C40" t="s">
-        <v>170</v>
+        <v>410</v>
       </c>
       <c r="D40" t="s">
-        <v>171</v>
+        <v>422</v>
       </c>
       <c r="E40" t="s">
-        <v>172</v>
+        <v>411</v>
       </c>
       <c r="F40" t="s">
-        <v>173</v>
+        <v>418</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>412</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2589,22 +2639,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>175</v>
+        <v>410</v>
       </c>
       <c r="D41" t="s">
-        <v>176</v>
+        <v>423</v>
       </c>
       <c r="E41" t="s">
-        <v>177</v>
+        <v>413</v>
       </c>
       <c r="F41" t="s">
-        <v>178</v>
+        <v>419</v>
       </c>
       <c r="G41" t="s">
-        <v>179</v>
+        <v>414</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2612,22 +2662,22 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>180</v>
+        <v>410</v>
       </c>
       <c r="D42" t="s">
-        <v>181</v>
+        <v>424</v>
       </c>
       <c r="E42" t="s">
-        <v>182</v>
+        <v>415</v>
       </c>
       <c r="F42" t="s">
-        <v>183</v>
+        <v>420</v>
       </c>
       <c r="G42" t="s">
-        <v>184</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -2635,22 +2685,22 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="C43" t="s">
-        <v>185</v>
+        <v>157</v>
       </c>
       <c r="D43" t="s">
-        <v>186</v>
+        <v>425</v>
       </c>
       <c r="E43" t="s">
-        <v>187</v>
+        <v>416</v>
       </c>
       <c r="F43" t="s">
-        <v>188</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>82</v>
+        <v>421</v>
+      </c>
+      <c r="G43" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2658,22 +2708,22 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="C44" t="s">
-        <v>194</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
-        <v>195</v>
+        <v>426</v>
       </c>
       <c r="E44" t="s">
-        <v>304</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>82</v>
+        <v>417</v>
+      </c>
+      <c r="F44" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -2681,22 +2731,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C45" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="D45" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="E45" t="s">
-        <v>305</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>82</v>
+        <v>172</v>
+      </c>
+      <c r="F45" t="s">
+        <v>173</v>
+      </c>
+      <c r="G45" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2704,22 +2754,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C46" t="s">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="D46" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="E46" t="s">
-        <v>200</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>82</v>
+        <v>177</v>
+      </c>
+      <c r="F46" t="s">
+        <v>178</v>
+      </c>
+      <c r="G46" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2727,22 +2777,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C47" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
       <c r="D47" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="E47" t="s">
-        <v>306</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>82</v>
+        <v>182</v>
+      </c>
+      <c r="F47" t="s">
+        <v>183</v>
+      </c>
+      <c r="G47" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2750,19 +2800,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="C48" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="D48" t="s">
-        <v>204</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>82</v>
+        <v>186</v>
+      </c>
+      <c r="E48" t="s">
+        <v>187</v>
+      </c>
+      <c r="F48" t="s">
+        <v>188</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>82</v>
@@ -2776,13 +2826,13 @@
         <v>193</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="D49" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E49" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>82</v>
@@ -2799,13 +2849,13 @@
         <v>193</v>
       </c>
       <c r="C50" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D50" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="E50" t="s">
-        <v>209</v>
+        <v>305</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>82</v>
@@ -2822,13 +2872,13 @@
         <v>193</v>
       </c>
       <c r="C51" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D51" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="E51" t="s">
-        <v>308</v>
+        <v>200</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>82</v>
@@ -2845,13 +2895,13 @@
         <v>193</v>
       </c>
       <c r="C52" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D52" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E52" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>82</v>
@@ -2868,13 +2918,13 @@
         <v>193</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="D53" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E53" t="s">
-        <v>310</v>
+        <v>408</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>82</v>
@@ -2891,13 +2941,13 @@
         <v>193</v>
       </c>
       <c r="C54" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="D54" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E54" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>82</v>
@@ -2914,13 +2964,13 @@
         <v>193</v>
       </c>
       <c r="C55" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D55" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E55" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>82</v>
@@ -2937,13 +2987,13 @@
         <v>193</v>
       </c>
       <c r="C56" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D56" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E56" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>82</v>
@@ -2960,13 +3010,13 @@
         <v>193</v>
       </c>
       <c r="C57" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="D57" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="E57" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>82</v>
@@ -2983,13 +3033,13 @@
         <v>193</v>
       </c>
       <c r="C58" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="D58" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="E58" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>82</v>
@@ -3006,13 +3056,13 @@
         <v>193</v>
       </c>
       <c r="C59" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D59" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E59" t="s">
-        <v>229</v>
+        <v>311</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>82</v>
@@ -3029,13 +3079,13 @@
         <v>193</v>
       </c>
       <c r="C60" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="D60" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="E60" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>82</v>
@@ -3052,13 +3102,13 @@
         <v>193</v>
       </c>
       <c r="C61" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="D61" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="E61" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>82</v>
@@ -3075,13 +3125,13 @@
         <v>193</v>
       </c>
       <c r="C62" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="D62" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="E62" t="s">
-        <v>237</v>
+        <v>313</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>82</v>
@@ -3098,13 +3148,13 @@
         <v>193</v>
       </c>
       <c r="C63" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="D63" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="E63" t="s">
-        <v>240</v>
+        <v>314</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>82</v>
@@ -3121,13 +3171,13 @@
         <v>193</v>
       </c>
       <c r="C64" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="D64" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="E64" t="s">
-        <v>316</v>
+        <v>229</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>82</v>
@@ -3144,13 +3194,13 @@
         <v>193</v>
       </c>
       <c r="C65" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="D65" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="E65" t="s">
-        <v>317</v>
+        <v>232</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>82</v>
@@ -3167,13 +3217,13 @@
         <v>193</v>
       </c>
       <c r="C66" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="D66" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E66" t="s">
-        <v>247</v>
+        <v>315</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>82</v>
@@ -3190,13 +3240,13 @@
         <v>193</v>
       </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="D67" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="E67" t="s">
-        <v>318</v>
+        <v>237</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>82</v>
@@ -3213,13 +3263,13 @@
         <v>193</v>
       </c>
       <c r="C68" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="D68" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="E68" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>82</v>
@@ -3236,13 +3286,13 @@
         <v>193</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="D69" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="E69" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>82</v>
@@ -3259,13 +3309,13 @@
         <v>193</v>
       </c>
       <c r="C70" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="D70" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E70" t="s">
-        <v>257</v>
+        <v>317</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>82</v>
@@ -3282,13 +3332,13 @@
         <v>193</v>
       </c>
       <c r="C71" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="D71" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="E71" t="s">
-        <v>320</v>
+        <v>247</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>82</v>
@@ -3305,13 +3355,13 @@
         <v>193</v>
       </c>
       <c r="C72" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D72" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="E72" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>82</v>
@@ -3328,13 +3378,13 @@
         <v>193</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D73" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="E73" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>82</v>
@@ -3351,13 +3401,13 @@
         <v>193</v>
       </c>
       <c r="C74" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="D74" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E74" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>82</v>
@@ -3374,13 +3424,13 @@
         <v>193</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D75" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="E75" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>82</v>
@@ -3397,13 +3447,13 @@
         <v>193</v>
       </c>
       <c r="C76" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D76" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="E76" t="s">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>82</v>
@@ -3420,13 +3470,13 @@
         <v>193</v>
       </c>
       <c r="C77" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>274</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>82</v>
+        <v>261</v>
+      </c>
+      <c r="E77" t="s">
+        <v>321</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>82</v>
@@ -3443,13 +3493,13 @@
         <v>193</v>
       </c>
       <c r="C78" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="D78" t="s">
-        <v>409</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>82</v>
+        <v>263</v>
+      </c>
+      <c r="E78" t="s">
+        <v>264</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>82</v>
@@ -3466,13 +3516,13 @@
         <v>193</v>
       </c>
       <c r="C79" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="D79" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="E79" t="s">
-        <v>278</v>
+        <v>322</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>82</v>
@@ -3483,19 +3533,19 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" t="s">
         <v>193</v>
       </c>
       <c r="C80" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D80" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="E80" t="s">
-        <v>323</v>
+        <v>269</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>82</v>
@@ -3506,19 +3556,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81" t="s">
         <v>193</v>
       </c>
       <c r="C81" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="D81" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="E81" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>82</v>
@@ -3529,19 +3579,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82" t="s">
         <v>193</v>
       </c>
       <c r="C82" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="D82" t="s">
-        <v>285</v>
-      </c>
-      <c r="E82" t="s">
-        <v>286</v>
+        <v>274</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>82</v>
@@ -3552,19 +3602,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83" t="s">
         <v>193</v>
       </c>
       <c r="C83" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D83" t="s">
-        <v>288</v>
-      </c>
-      <c r="E83" t="s">
-        <v>289</v>
+        <v>409</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>82</v>
@@ -3575,19 +3625,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84" t="s">
         <v>193</v>
       </c>
       <c r="C84" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="D84" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="E84" t="s">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>82</v>
@@ -3598,19 +3648,19 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85" t="s">
         <v>193</v>
       </c>
       <c r="C85" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="D85" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="E85" t="s">
-        <v>294</v>
+        <v>323</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>82</v>
@@ -3621,19 +3671,19 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86" t="s">
         <v>193</v>
       </c>
       <c r="C86" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="D86" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="E86" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>82</v>
@@ -3644,19 +3694,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87" t="s">
         <v>193</v>
       </c>
       <c r="C87" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="D87" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="E87" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>82</v>
@@ -3667,19 +3717,19 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88" t="s">
         <v>193</v>
       </c>
       <c r="C88" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="D88" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="E88" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>82</v>
@@ -3690,634 +3740,729 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>326</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>328</v>
+        <v>193</v>
+      </c>
+      <c r="C89" t="s">
+        <v>290</v>
+      </c>
+      <c r="D89" t="s">
+        <v>291</v>
       </c>
       <c r="E89" t="s">
-        <v>329</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="G89" t="s">
-        <v>331</v>
+        <v>324</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>326</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>333</v>
+        <v>193</v>
+      </c>
+      <c r="C90" t="s">
+        <v>292</v>
+      </c>
+      <c r="D90" t="s">
+        <v>293</v>
       </c>
       <c r="E90" t="s">
-        <v>334</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G90" t="s">
-        <v>336</v>
+        <v>294</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>326</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>338</v>
+        <v>193</v>
+      </c>
+      <c r="C91" t="s">
+        <v>295</v>
+      </c>
+      <c r="D91" t="s">
+        <v>296</v>
       </c>
       <c r="E91" t="s">
-        <v>339</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G91" t="s">
-        <v>336</v>
+        <v>297</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>326</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>341</v>
+        <v>193</v>
+      </c>
+      <c r="C92" t="s">
+        <v>298</v>
+      </c>
+      <c r="D92" t="s">
+        <v>299</v>
       </c>
       <c r="E92" t="s">
-        <v>342</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G92" t="s">
-        <v>336</v>
+        <v>300</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>326</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>344</v>
+        <v>193</v>
+      </c>
+      <c r="C93" t="s">
+        <v>301</v>
+      </c>
+      <c r="D93" t="s">
+        <v>302</v>
       </c>
       <c r="E93" t="s">
-        <v>345</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="G93" t="s">
-        <v>347</v>
+        <v>303</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94" t="s">
         <v>326</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="E94" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
       <c r="G94" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>376</v>
-      </c>
-      <c r="C95" t="s">
-        <v>355</v>
-      </c>
-      <c r="D95" t="s">
-        <v>356</v>
+        <v>326</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="E95" t="s">
-        <v>357</v>
-      </c>
-      <c r="F95" t="s">
-        <v>358</v>
+        <v>334</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="G95" t="s">
-        <v>359</v>
+        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>376</v>
-      </c>
-      <c r="C96" t="s">
-        <v>360</v>
-      </c>
-      <c r="D96" t="s">
-        <v>361</v>
+        <v>326</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>338</v>
       </c>
       <c r="E96" t="s">
-        <v>362</v>
-      </c>
-      <c r="F96" t="s">
-        <v>44</v>
+        <v>339</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="G96" t="s">
-        <v>44</v>
+        <v>336</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>376</v>
-      </c>
-      <c r="C97" t="s">
-        <v>363</v>
-      </c>
-      <c r="D97" t="s">
-        <v>364</v>
+        <v>326</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="E97" t="s">
-        <v>365</v>
-      </c>
-      <c r="F97" t="s">
-        <v>366</v>
+        <v>342</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="G97" t="s">
-        <v>367</v>
+        <v>336</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>376</v>
-      </c>
-      <c r="C98" t="s">
-        <v>368</v>
-      </c>
-      <c r="D98" t="s">
-        <v>369</v>
+        <v>326</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="E98" t="s">
-        <v>370</v>
-      </c>
-      <c r="F98" t="s">
-        <v>371</v>
+        <v>345</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="G98" t="s">
-        <v>372</v>
+        <v>347</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>376</v>
-      </c>
-      <c r="C99" t="s">
-        <v>373</v>
-      </c>
-      <c r="D99" t="s">
-        <v>374</v>
+        <v>326</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>349</v>
       </c>
       <c r="E99" t="s">
-        <v>375</v>
-      </c>
-      <c r="F99" t="s">
-        <v>44</v>
+        <v>350</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="G99" t="s">
-        <v>44</v>
+        <v>352</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="C100" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="D100" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="E100" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="F100" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="G100" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="C101" t="s">
-        <v>382</v>
+        <v>360</v>
       </c>
       <c r="D101" t="s">
-        <v>383</v>
+        <v>361</v>
       </c>
       <c r="E101" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="F101" t="s">
-        <v>385</v>
+        <v>44</v>
       </c>
       <c r="G101" t="s">
-        <v>386</v>
+        <v>44</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="C102" t="s">
-        <v>387</v>
+        <v>363</v>
       </c>
       <c r="D102" t="s">
-        <v>388</v>
+        <v>364</v>
       </c>
       <c r="E102" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="F102" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="G102" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="C103" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="D103" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="E103" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="F103" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="G103" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="C104" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="D104" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="E104" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="F104" t="s">
-        <v>400</v>
+        <v>44</v>
       </c>
       <c r="G104" t="s">
-        <v>401</v>
+        <v>44</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105" t="s">
         <v>407</v>
       </c>
       <c r="C105" t="s">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="D105" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="E105" t="s">
-        <v>404</v>
+        <v>379</v>
       </c>
       <c r="F105" t="s">
-        <v>405</v>
+        <v>380</v>
       </c>
       <c r="G105" t="s">
-        <v>406</v>
+        <v>381</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>407</v>
+      </c>
+      <c r="C106" t="s">
+        <v>382</v>
+      </c>
+      <c r="D106" t="s">
+        <v>383</v>
+      </c>
+      <c r="E106" t="s">
+        <v>384</v>
+      </c>
+      <c r="F106" t="s">
+        <v>385</v>
+      </c>
+      <c r="G106" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>107</v>
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>407</v>
+      </c>
+      <c r="C107" t="s">
+        <v>387</v>
+      </c>
+      <c r="D107" t="s">
+        <v>388</v>
+      </c>
+      <c r="E107" t="s">
+        <v>389</v>
+      </c>
+      <c r="F107" t="s">
+        <v>390</v>
+      </c>
+      <c r="G107" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>108</v>
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>407</v>
+      </c>
+      <c r="C108" t="s">
+        <v>392</v>
+      </c>
+      <c r="D108" t="s">
+        <v>393</v>
+      </c>
+      <c r="E108" t="s">
+        <v>394</v>
+      </c>
+      <c r="F108" t="s">
+        <v>395</v>
+      </c>
+      <c r="G108" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>109</v>
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>407</v>
+      </c>
+      <c r="C109" t="s">
+        <v>397</v>
+      </c>
+      <c r="D109" t="s">
+        <v>398</v>
+      </c>
+      <c r="E109" t="s">
+        <v>399</v>
+      </c>
+      <c r="F109" t="s">
+        <v>400</v>
+      </c>
+      <c r="G109" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>110</v>
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>407</v>
+      </c>
+      <c r="C110" t="s">
+        <v>402</v>
+      </c>
+      <c r="D110" t="s">
+        <v>403</v>
+      </c>
+      <c r="E110" t="s">
+        <v>404</v>
+      </c>
+      <c r="F110" t="s">
+        <v>405</v>
+      </c>
+      <c r="G110" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151">
         <v>150</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E89" r:id="rId1" display="mailto:miriam.sotov@redsalud.gob.cl" xr:uid="{CA864F29-52B2-43C7-A13E-76AEC8A49A4F}"/>
-    <hyperlink ref="G89" r:id="rId2" display="mailto:sandra.felipe@redsalud.gob.cl" xr:uid="{E976CC02-5359-4441-A979-BD71659626F9}"/>
-    <hyperlink ref="E90" r:id="rId3" display="mailto:mariela.gallardo@redsalud.gob.cl" xr:uid="{9C732FB4-A61F-4E39-B898-750F2EC775F1}"/>
-    <hyperlink ref="G90" r:id="rId4" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{C4E3479B-2B05-4DD8-8E11-9D8BF2B85E31}"/>
-    <hyperlink ref="E91" r:id="rId5" display="mailto:valentina.molinah@redsalud.gob.cl" xr:uid="{C1ADBA44-5B7A-4977-AABE-11063BE1B6A7}"/>
-    <hyperlink ref="G91" r:id="rId6" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{D04DDA16-E51A-4689-BBD7-423B1C3B374F}"/>
-    <hyperlink ref="E92" r:id="rId7" display="mailto:ariel.davila.q@redsalud.gob.cl" xr:uid="{EC233077-E60B-496D-AE88-C023286395AA}"/>
-    <hyperlink ref="G92" r:id="rId8" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{83E83D38-31B5-4021-9A85-A21840781BD6}"/>
-    <hyperlink ref="E93" r:id="rId9" display="mailto:veronica.perez.gutierrez@redsalud.gob.cl" xr:uid="{FA6F0642-EBF9-4CD6-9C47-58B1F0F3E6C0}"/>
-    <hyperlink ref="G93" r:id="rId10" display="mailto:adriana.toledo@redsalud.gob.cl" xr:uid="{CD766FCC-3306-4798-96D5-1B84D28ECDC6}"/>
-    <hyperlink ref="E94" r:id="rId11" display="mailto:romy.geissbuhler@redsalud.gob.cl" xr:uid="{7D4D5B0A-0E35-49DA-AA2E-78A73F7C081E}"/>
-    <hyperlink ref="G94" r:id="rId12" display="mailto:marisol.lara@redsalud.gob.cl" xr:uid="{49F93AE7-78F6-409A-802B-D4EFCB8ABFD3}"/>
+    <hyperlink ref="E94" r:id="rId1" display="mailto:miriam.sotov@redsalud.gob.cl" xr:uid="{CA864F29-52B2-43C7-A13E-76AEC8A49A4F}"/>
+    <hyperlink ref="G94" r:id="rId2" display="mailto:sandra.felipe@redsalud.gob.cl" xr:uid="{E976CC02-5359-4441-A979-BD71659626F9}"/>
+    <hyperlink ref="E95" r:id="rId3" display="mailto:mariela.gallardo@redsalud.gob.cl" xr:uid="{9C732FB4-A61F-4E39-B898-750F2EC775F1}"/>
+    <hyperlink ref="G95" r:id="rId4" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{C4E3479B-2B05-4DD8-8E11-9D8BF2B85E31}"/>
+    <hyperlink ref="E96" r:id="rId5" display="mailto:valentina.molinah@redsalud.gob.cl" xr:uid="{C1ADBA44-5B7A-4977-AABE-11063BE1B6A7}"/>
+    <hyperlink ref="G96" r:id="rId6" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{D04DDA16-E51A-4689-BBD7-423B1C3B374F}"/>
+    <hyperlink ref="E97" r:id="rId7" display="mailto:ariel.davila.q@redsalud.gob.cl" xr:uid="{EC233077-E60B-496D-AE88-C023286395AA}"/>
+    <hyperlink ref="G97" r:id="rId8" display="mailto:iris.reyes@redsalud.gob.cl" xr:uid="{83E83D38-31B5-4021-9A85-A21840781BD6}"/>
+    <hyperlink ref="E98" r:id="rId9" display="mailto:veronica.perez.gutierrez@redsalud.gob.cl" xr:uid="{FA6F0642-EBF9-4CD6-9C47-58B1F0F3E6C0}"/>
+    <hyperlink ref="G98" r:id="rId10" display="mailto:adriana.toledo@redsalud.gob.cl" xr:uid="{CD766FCC-3306-4798-96D5-1B84D28ECDC6}"/>
+    <hyperlink ref="E99" r:id="rId11" display="mailto:romy.geissbuhler@redsalud.gob.cl" xr:uid="{7D4D5B0A-0E35-49DA-AA2E-78A73F7C081E}"/>
+    <hyperlink ref="G99" r:id="rId12" display="mailto:marisol.lara@redsalud.gob.cl" xr:uid="{49F93AE7-78F6-409A-802B-D4EFCB8ABFD3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FCB9C4-B7EF-4B34-80F4-B134BB523657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049297CA-28BD-439E-97B4-DA63C19BA59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="456">
   <si>
     <t>id</t>
   </si>
@@ -246,42 +246,27 @@
     <t>cr. ambulatorio</t>
   </si>
   <si>
-    <t>srta. lya reyes carreño</t>
-  </si>
-  <si>
     <t>lya.reyes@redsalud.gob.cl</t>
   </si>
   <si>
     <t>eficiencia clínica hospitalaria</t>
   </si>
   <si>
-    <t>mat. katherinne kupferschmidt silva</t>
-  </si>
-  <si>
     <t>katherinne.kupferschmidt@redsalud.gob.cl</t>
   </si>
   <si>
-    <t>mat. claudia neira</t>
-  </si>
-  <si>
     <t>claudia.neira@redsalud.gob.cl</t>
   </si>
   <si>
     <t>gestión de la demanda</t>
   </si>
   <si>
-    <t>eu. ana karina henriquez zamorano</t>
-  </si>
-  <si>
     <t>anakarina.henriquez@redsalud.gob.cl</t>
   </si>
   <si>
     <t>gestión de pacientes</t>
   </si>
   <si>
-    <t>eu. valesska gonzalez toro</t>
-  </si>
-  <si>
     <t>valesska.gonzalez@redsalud.gob.cl</t>
   </si>
   <si>
@@ -408,9 +393,6 @@
     <t>rosario.castilloj@redsalud.gob.cl</t>
   </si>
   <si>
-    <t>flga. valentina román</t>
-  </si>
-  <si>
     <t>valentina.roman.m@redsalud.gob.cl</t>
   </si>
   <si>
@@ -447,9 +429,6 @@
     <t>some</t>
   </si>
   <si>
-    <t>eu. daniela calderon avendaño</t>
-  </si>
-  <si>
     <t>daniela.calderon@redsalud.gob.cl</t>
   </si>
   <si>
@@ -744,9 +723,6 @@
     <t>karina aguirre sepúlveda</t>
   </si>
   <si>
-    <t>unidad de cuidados intensivos críticos</t>
-  </si>
-  <si>
     <t>daniela rebolledo oyarzo</t>
   </si>
   <si>
@@ -945,12 +921,6 @@
     <t>cuidados policlínico cardiológico</t>
   </si>
   <si>
-    <t>daniela fuenzalida andrade</t>
-  </si>
-  <si>
-    <t>daniela.fuenzalida@redsalud.gob.cl</t>
-  </si>
-  <si>
     <t>liliana.vegae@redsalud.gob.cl</t>
   </si>
   <si>
@@ -1318,6 +1288,123 @@
   </si>
   <si>
     <t xml:space="preserve">camila catalina figueroa villagra </t>
+  </si>
+  <si>
+    <t>paula gomez</t>
+  </si>
+  <si>
+    <t>paula.gomez.c@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>maría josé abarca aguirre</t>
+  </si>
+  <si>
+    <t>regina espinoza sepúlveda</t>
+  </si>
+  <si>
+    <t>regina.sepulveda@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>delfina villalobos guzmán</t>
+  </si>
+  <si>
+    <t>nefrologia.sanjuan@gmail.com</t>
+  </si>
+  <si>
+    <t>marisol carrera pérez</t>
+  </si>
+  <si>
+    <t>patricia toro moya</t>
+  </si>
+  <si>
+    <t>patricia.toro.m@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>litta fuentealba flores</t>
+  </si>
+  <si>
+    <t>litta.fuentealba@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>paolaa.rojas@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>paola rojas chacan</t>
+  </si>
+  <si>
+    <t>unidad de cuidados intensivos (uci)</t>
+  </si>
+  <si>
+    <t>sandra silva gavilán</t>
+  </si>
+  <si>
+    <t>pamela.fonseca@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>nicole.mora@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>melany.argandona@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>nicol.ramirez.m@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>matilda sepúlveda</t>
+  </si>
+  <si>
+    <t>matilda.sepulveda.a@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>melany argandoña </t>
+  </si>
+  <si>
+    <t>nicole mora</t>
+  </si>
+  <si>
+    <t>pamela fonseca</t>
+  </si>
+  <si>
+    <t>nicol ramírez</t>
+  </si>
+  <si>
+    <t>carol.trincado@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>carol trincado garrido</t>
+  </si>
+  <si>
+    <t>alejandra.padilla@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>daniela.navarreter@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>daniela navarrete</t>
+  </si>
+  <si>
+    <t>ana karina henriquez zamorano</t>
+  </si>
+  <si>
+    <t>valesska gonzalez toro</t>
+  </si>
+  <si>
+    <t>daniela calderon avendaño</t>
+  </si>
+  <si>
+    <t>valentina román</t>
+  </si>
+  <si>
+    <t>lya reyes carreño</t>
+  </si>
+  <si>
+    <t>katherinne kupferschmidt silva</t>
+  </si>
+  <si>
+    <t>claudia neira</t>
+  </si>
+  <si>
+    <t>susana. nuñezv@redsalud.gob.cl</t>
   </si>
 </sst>
 </file>
@@ -1359,12 +1446,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1716,10 +1804,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
@@ -1742,10 +1830,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -1765,10 +1853,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1788,10 +1876,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
         <v>63</v>
@@ -1811,10 +1899,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D5" t="s">
         <v>64</v>
@@ -1834,10 +1922,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D6" t="s">
         <v>65</v>
@@ -1857,10 +1945,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C7" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1880,10 +1968,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C8" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
@@ -1903,10 +1991,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
         <v>31</v>
@@ -1926,10 +2014,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D10" t="s">
         <v>66</v>
@@ -1949,10 +2037,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C11" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
@@ -1972,10 +2060,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
         <v>42</v>
@@ -1995,10 +2083,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D13" t="s">
         <v>45</v>
@@ -2018,10 +2106,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C14" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D14" t="s">
         <v>49</v>
@@ -2041,10 +2129,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
         <v>53</v>
@@ -2064,7 +2152,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C16" t="s">
         <v>55</v>
@@ -2087,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
@@ -2110,7 +2198,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C18" t="s">
         <v>60</v>
@@ -2133,16 +2221,16 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C19" t="s">
         <v>68</v>
       </c>
       <c r="D19" t="s">
+        <v>452</v>
+      </c>
+      <c r="E19" t="s">
         <v>69</v>
-      </c>
-      <c r="E19" t="s">
-        <v>70</v>
       </c>
       <c r="F19" t="s">
         <v>44</v>
@@ -2156,16 +2244,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>453</v>
+      </c>
+      <c r="E20" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" t="s">
-        <v>73</v>
       </c>
       <c r="F20" t="s">
         <v>44</v>
@@ -2179,16 +2267,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>454</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
         <v>44</v>
@@ -2202,16 +2290,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="E22" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
         <v>44</v>
@@ -2225,16 +2313,16 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>449</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s">
         <v>44</v>
@@ -2248,22 +2336,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D24" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="E24" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F24" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="G24" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2271,22 +2359,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C25" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D25" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="E25" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -2294,22 +2382,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -2317,22 +2405,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -2340,22 +2428,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="F28" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G28" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -2363,16 +2451,16 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C29" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="E29" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F29" t="s">
         <v>44</v>
@@ -2386,22 +2474,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -2409,16 +2497,16 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" t="s">
         <v>140</v>
       </c>
-      <c r="C31" t="s">
-        <v>147</v>
-      </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E31" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="F31" t="s">
         <v>44</v>
@@ -2432,22 +2520,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C32" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2455,22 +2543,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C33" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F33" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G33" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2478,22 +2566,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D34" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E34" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2501,22 +2589,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C35" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F35" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2524,22 +2612,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>451</v>
       </c>
       <c r="E36" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2547,22 +2635,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C37" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E37" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F37" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G37" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2570,22 +2658,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C38" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="E38" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G38" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,22 +2681,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>450</v>
       </c>
       <c r="E39" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="F39" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -2616,22 +2704,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D40" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="E40" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="F40" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="G40" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -2639,22 +2727,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C41" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="D41" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E41" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="F41" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="G41" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -2662,19 +2750,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C42" t="s">
+        <v>400</v>
+      </c>
+      <c r="D42" t="s">
+        <v>414</v>
+      </c>
+      <c r="E42" t="s">
+        <v>405</v>
+      </c>
+      <c r="F42" t="s">
         <v>410</v>
-      </c>
-      <c r="D42" t="s">
-        <v>424</v>
-      </c>
-      <c r="E42" t="s">
-        <v>415</v>
-      </c>
-      <c r="F42" t="s">
-        <v>420</v>
       </c>
       <c r="G42" t="s">
         <v>19</v>
@@ -2685,19 +2773,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D43" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="E43" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="F43" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="G43" t="s">
         <v>9</v>
@@ -2708,16 +2796,16 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C44" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D44" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="E44" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="F44" t="s">
         <v>44</v>
@@ -2731,22 +2819,22 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C45" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="F45" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -2754,22 +2842,22 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>162</v>
+      </c>
+      <c r="C46" t="s">
+        <v>168</v>
+      </c>
+      <c r="D46" t="s">
         <v>169</v>
       </c>
-      <c r="C46" t="s">
-        <v>175</v>
-      </c>
-      <c r="D46" t="s">
-        <v>176</v>
-      </c>
       <c r="E46" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F46" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G46" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -2777,22 +2865,22 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C47" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D47" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E47" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F47" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G47" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -2800,22 +2888,22 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="C48" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D48" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E48" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F48" t="s">
-        <v>188</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>82</v>
+        <v>181</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -2823,22 +2911,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C49" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D49" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E49" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2846,22 +2934,22 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C50" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E50" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2869,22 +2957,22 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>186</v>
+      </c>
+      <c r="C51" t="s">
+        <v>191</v>
+      </c>
+      <c r="D51" t="s">
+        <v>192</v>
+      </c>
+      <c r="E51" t="s">
         <v>193</v>
       </c>
-      <c r="C51" t="s">
-        <v>198</v>
-      </c>
-      <c r="D51" t="s">
-        <v>199</v>
-      </c>
-      <c r="E51" t="s">
-        <v>200</v>
-      </c>
       <c r="F51" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -2892,22 +2980,22 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C52" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D52" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E52" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2915,22 +3003,22 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C53" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="D53" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E53" t="s">
-        <v>408</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>82</v>
+        <v>398</v>
+      </c>
+      <c r="F53" t="s">
+        <v>417</v>
+      </c>
+      <c r="G53" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2938,22 +3026,22 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C54" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="D54" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E54" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2961,22 +3049,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C55" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D55" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E55" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2984,22 +3072,22 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C56" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D56" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E56" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3007,22 +3095,22 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C57" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D57" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E57" t="s">
-        <v>309</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>82</v>
+        <v>299</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -3030,22 +3118,22 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C58" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D58" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E58" t="s">
-        <v>310</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>82</v>
+        <v>300</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -3053,22 +3141,22 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C59" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E59" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3076,22 +3164,22 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C60" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D60" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E60" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3099,22 +3187,22 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C61" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="D61" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E61" t="s">
-        <v>312</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>82</v>
+        <v>302</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -3122,22 +3210,22 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C62" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D62" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E62" t="s">
-        <v>313</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>82</v>
+        <v>303</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -3145,22 +3233,22 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C63" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="D63" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E63" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3168,22 +3256,22 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C64" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="D64" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E64" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3191,22 +3279,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C65" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D65" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E65" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3214,22 +3302,22 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="D66" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E66" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3237,22 +3325,22 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C67" t="s">
-        <v>235</v>
+        <v>431</v>
       </c>
       <c r="D67" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="E67" t="s">
-        <v>237</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>82</v>
+        <v>229</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -3260,22 +3348,22 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C68" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D68" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="E68" t="s">
-        <v>240</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G68" s="1" t="s">
-        <v>82</v>
+        <v>232</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -3283,22 +3371,22 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C69" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="D69" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="E69" t="s">
-        <v>316</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G69" s="1" t="s">
-        <v>82</v>
+        <v>306</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -3306,22 +3394,22 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C70" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="D70" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="E70" t="s">
-        <v>317</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>82</v>
+        <v>307</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -3329,22 +3417,22 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C71" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D71" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="E71" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3352,22 +3440,22 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C72" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="D72" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="E72" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3375,22 +3463,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C73" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D73" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E73" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3398,22 +3486,22 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C74" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D74" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="E74" t="s">
-        <v>319</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>82</v>
+        <v>309</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -3421,22 +3509,22 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C75" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="D75" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="E75" t="s">
-        <v>257</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>82</v>
+        <v>249</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -3444,22 +3532,22 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C76" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="D76" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="E76" t="s">
-        <v>320</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>82</v>
+        <v>310</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -3467,22 +3555,22 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C77" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D77" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="E77" t="s">
-        <v>321</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>82</v>
+        <v>311</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -3490,22 +3578,22 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C78" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="D78" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E78" t="s">
-        <v>264</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G78" s="1" t="s">
-        <v>82</v>
+        <v>256</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -3513,22 +3601,22 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C79" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="D79" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E79" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3536,22 +3624,22 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D80" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="E80" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3559,22 +3647,22 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C81" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="D81" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="E81" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -3582,22 +3670,22 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C82" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="D82" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -3605,22 +3693,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C83" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="D83" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3628,22 +3716,22 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C84" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="E84" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3651,22 +3739,22 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C85" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="D85" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E85" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3674,22 +3762,22 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C86" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="D86" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E86" t="s">
-        <v>283</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G86" s="1" t="s">
-        <v>82</v>
+        <v>275</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -3697,22 +3785,22 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="D87" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E87" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -3720,22 +3808,22 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C88" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="D88" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E88" t="s">
-        <v>289</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>82</v>
+        <v>281</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -3743,22 +3831,22 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C89" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="D89" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E89" t="s">
-        <v>324</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>82</v>
+        <v>314</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -3766,22 +3854,22 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C90" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D90" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E90" t="s">
-        <v>294</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G90" s="1" t="s">
-        <v>82</v>
+        <v>286</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -3789,22 +3877,22 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C91" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D91" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="E91" t="s">
-        <v>297</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G91" s="1" t="s">
-        <v>82</v>
+        <v>289</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -3812,22 +3900,22 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C92" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="D92" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="E92" t="s">
-        <v>300</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>82</v>
+        <v>292</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -3835,22 +3923,22 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C93" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="D93" t="s">
-        <v>302</v>
+        <v>442</v>
       </c>
       <c r="E93" t="s">
-        <v>303</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>82</v>
+        <v>436</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -3858,22 +3946,22 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E94" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="G94" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -3881,22 +3969,22 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>316</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E95" t="s">
+        <v>324</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G95" t="s">
         <v>326</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E95" t="s">
-        <v>334</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G95" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -3904,22 +3992,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>316</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E96" t="s">
+        <v>329</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G96" t="s">
         <v>326</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E96" t="s">
-        <v>339</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G96" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -3927,22 +4015,22 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>316</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E97" t="s">
+        <v>332</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G97" t="s">
         <v>326</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E97" t="s">
-        <v>342</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G97" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -3950,22 +4038,22 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="E98" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="G98" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -3973,22 +4061,22 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="E99" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="G99" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -3996,22 +4084,22 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C100" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="D100" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="E100" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="F100" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="G100" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -4019,16 +4107,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C101" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D101" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E101" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="F101" t="s">
         <v>44</v>
@@ -4042,22 +4130,22 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C102" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E102" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="F102" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G102" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -4065,22 +4153,22 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C103" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="D103" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="E103" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="F103" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="G103" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -4088,16 +4176,16 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="C104" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="D104" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="E104" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F104" t="s">
         <v>44</v>
@@ -4111,22 +4199,22 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C105" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="D105" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E105" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="F105" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="G105" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -4134,22 +4222,22 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C106" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D106" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="E106" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F106" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G106" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -4157,22 +4245,22 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C107" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="D107" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="E107" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="F107" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="G107" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -4180,22 +4268,22 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C108" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D108" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="E108" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="F108" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G108" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -4203,22 +4291,22 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C109" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D109" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="E109" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="F109" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G109" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -4226,22 +4314,22 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="C110" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="D110" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="E110" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="F110" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="G110" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">

--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049297CA-28BD-439E-97B4-DA63C19BA59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8C5649-DB4D-4001-9861-9154EB91F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="463">
   <si>
     <t>id</t>
   </si>
@@ -1405,6 +1405,27 @@
   </si>
   <si>
     <t>susana. nuñezv@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jose.molina.a@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>carolina.ruz.r@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>claudia reyes cofré</t>
+  </si>
+  <si>
+    <t>patricia.villegas.u@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>patricia villegas urrutia</t>
+  </si>
+  <si>
+    <t>paola.guadalupe@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>paola guadalupe</t>
   </si>
 </sst>
 </file>
@@ -2902,7 +2923,7 @@
       <c r="F48" t="s">
         <v>181</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" t="s">
         <v>445</v>
       </c>
     </row>
@@ -2991,11 +3012,11 @@
       <c r="E52" t="s">
         <v>296</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>77</v>
+      <c r="F52" t="s">
+        <v>417</v>
+      </c>
+      <c r="G52" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -3037,10 +3058,10 @@
       <c r="E54" t="s">
         <v>297</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" t="s">
         <v>444</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" t="s">
         <v>443</v>
       </c>
     </row>
@@ -3060,11 +3081,11 @@
       <c r="E55" t="s">
         <v>202</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>77</v>
+      <c r="F55" t="s">
+        <v>417</v>
+      </c>
+      <c r="G55" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -3083,11 +3104,11 @@
       <c r="E56" t="s">
         <v>298</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>77</v>
+      <c r="F56" t="s">
+        <v>458</v>
+      </c>
+      <c r="G56" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -3106,10 +3127,10 @@
       <c r="E57" t="s">
         <v>299</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F57" t="s">
         <v>427</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" t="s">
         <v>428</v>
       </c>
     </row>
@@ -3129,10 +3150,10 @@
       <c r="E58" t="s">
         <v>300</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F58" t="s">
         <v>427</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" t="s">
         <v>428</v>
       </c>
     </row>
@@ -3152,11 +3173,11 @@
       <c r="E59" t="s">
         <v>301</v>
       </c>
-      <c r="F59" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>77</v>
+      <c r="F59" t="s">
+        <v>427</v>
+      </c>
+      <c r="G59" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -3175,11 +3196,11 @@
       <c r="E60" t="s">
         <v>213</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>77</v>
+      <c r="F60" t="s">
+        <v>460</v>
+      </c>
+      <c r="G60" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -3198,10 +3219,10 @@
       <c r="E61" t="s">
         <v>302</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="F61" t="s">
         <v>419</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3221,10 +3242,10 @@
       <c r="E62" t="s">
         <v>303</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F62" t="s">
         <v>77</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" t="s">
         <v>455</v>
       </c>
     </row>
@@ -3244,11 +3265,11 @@
       <c r="E63" t="s">
         <v>304</v>
       </c>
-      <c r="F63" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>77</v>
+      <c r="F63" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -3267,11 +3288,11 @@
       <c r="E64" t="s">
         <v>222</v>
       </c>
-      <c r="F64" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>77</v>
+      <c r="F64" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -3290,11 +3311,11 @@
       <c r="E65" t="s">
         <v>225</v>
       </c>
-      <c r="F65" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>77</v>
+      <c r="F65" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -3336,10 +3357,10 @@
       <c r="E67" t="s">
         <v>229</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="F67" t="s">
         <v>432</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3359,10 +3380,10 @@
       <c r="E68" t="s">
         <v>232</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F68" t="s">
         <v>425</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" t="s">
         <v>426</v>
       </c>
     </row>
@@ -3382,10 +3403,10 @@
       <c r="E69" t="s">
         <v>306</v>
       </c>
-      <c r="F69" s="3" t="s">
+      <c r="F69" t="s">
         <v>425</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" t="s">
         <v>426</v>
       </c>
     </row>
@@ -3405,10 +3426,10 @@
       <c r="E70" t="s">
         <v>307</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="F70" t="s">
         <v>447</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" t="s">
         <v>446</v>
       </c>
     </row>
@@ -3497,10 +3518,10 @@
       <c r="E74" t="s">
         <v>309</v>
       </c>
-      <c r="F74" s="3" t="s">
+      <c r="F74" t="s">
         <v>420</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" t="s">
         <v>421</v>
       </c>
     </row>
@@ -3520,10 +3541,10 @@
       <c r="E75" t="s">
         <v>249</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="F75" t="s">
         <v>420</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" t="s">
         <v>421</v>
       </c>
     </row>
@@ -3543,10 +3564,10 @@
       <c r="E76" t="s">
         <v>310</v>
       </c>
-      <c r="F76" s="3" t="s">
+      <c r="F76" t="s">
         <v>420</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" t="s">
         <v>421</v>
       </c>
     </row>
@@ -3566,10 +3587,10 @@
       <c r="E77" t="s">
         <v>311</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="F77" t="s">
         <v>422</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" t="s">
         <v>423</v>
       </c>
     </row>
@@ -3589,10 +3610,10 @@
       <c r="E78" t="s">
         <v>256</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="F78" t="s">
         <v>420</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" t="s">
         <v>421</v>
       </c>
     </row>
@@ -3612,11 +3633,11 @@
       <c r="E79" t="s">
         <v>312</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>77</v>
+      <c r="F79" t="s">
+        <v>44</v>
+      </c>
+      <c r="G79" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -3678,8 +3699,8 @@
       <c r="D82" t="s">
         <v>266</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>77</v>
+      <c r="E82" t="s">
+        <v>457</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>77</v>
@@ -3701,8 +3722,8 @@
       <c r="D83" t="s">
         <v>399</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>77</v>
+      <c r="E83" t="s">
+        <v>456</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>77</v>
@@ -3750,11 +3771,11 @@
       <c r="E85" t="s">
         <v>313</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G85" s="1" t="s">
-        <v>77</v>
+      <c r="F85" t="s">
+        <v>424</v>
+      </c>
+      <c r="G85" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -3773,10 +3794,10 @@
       <c r="E86" t="s">
         <v>275</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" t="s">
         <v>424</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3819,10 +3840,10 @@
       <c r="E88" t="s">
         <v>281</v>
       </c>
-      <c r="F88" s="3" t="s">
+      <c r="F88" t="s">
         <v>430</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" t="s">
         <v>429</v>
       </c>
     </row>
@@ -3842,10 +3863,10 @@
       <c r="E89" t="s">
         <v>314</v>
       </c>
-      <c r="F89" s="3" t="s">
+      <c r="F89" t="s">
         <v>36</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3865,10 +3886,10 @@
       <c r="E90" t="s">
         <v>286</v>
       </c>
-      <c r="F90" s="3" t="s">
+      <c r="F90" t="s">
         <v>441</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G90" t="s">
         <v>433</v>
       </c>
     </row>
@@ -3888,10 +3909,10 @@
       <c r="E91" t="s">
         <v>289</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F91" t="s">
         <v>440</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" t="s">
         <v>434</v>
       </c>
     </row>
@@ -3911,10 +3932,10 @@
       <c r="E92" t="s">
         <v>292</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F92" t="s">
         <v>439</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" t="s">
         <v>435</v>
       </c>
     </row>
@@ -3934,10 +3955,10 @@
       <c r="E93" t="s">
         <v>436</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F93" t="s">
         <v>437</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="G93" t="s">
         <v>438</v>
       </c>
     </row>
@@ -4551,6 +4572,7 @@
     <hyperlink ref="G98" r:id="rId10" display="mailto:adriana.toledo@redsalud.gob.cl" xr:uid="{CD766FCC-3306-4798-96D5-1B84D28ECDC6}"/>
     <hyperlink ref="E99" r:id="rId11" display="mailto:romy.geissbuhler@redsalud.gob.cl" xr:uid="{7D4D5B0A-0E35-49DA-AA2E-78A73F7C081E}"/>
     <hyperlink ref="G99" r:id="rId12" display="mailto:marisol.lara@redsalud.gob.cl" xr:uid="{49F93AE7-78F6-409A-802B-D4EFCB8ABFD3}"/>
+    <hyperlink ref="G60" r:id="rId13" xr:uid="{2F56BAFC-F029-46F8-AD9A-DA5CE063DFB2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
+++ b/2- BB.DD. SERVICIOS Y UNIDADES/BBDD SERVICIOS Y UNIDADES.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IPLACEX\Año 2\PRÁCTICA IPLACEX\PLATAFORMA PASANTÍAS\GITHUB\2- BB.DD. SERVICIOS Y UNIDADES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB8C5649-DB4D-4001-9861-9154EB91F88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCAF0BC-AC52-44CC-A732-892C4A8898AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7936E908-9EDA-4102-87A8-C4382552261F}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$H$151</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="471">
   <si>
     <t>id</t>
   </si>
@@ -1426,6 +1429,30 @@
   </si>
   <si>
     <t>paola guadalupe</t>
+  </si>
+  <si>
+    <t>marisol.carrera@redsalud.gob.cl </t>
+  </si>
+  <si>
+    <t>Marisol Carrera</t>
+  </si>
+  <si>
+    <t>nadia.valdes@redsalud.gob.cl </t>
+  </si>
+  <si>
+    <t>nadia valdés moreno</t>
+  </si>
+  <si>
+    <t>christian warren eaton barrio</t>
+  </si>
+  <si>
+    <t>christian.eaton@gmail.com</t>
+  </si>
+  <si>
+    <t>jennifer.llano@redsalud.gob.cl</t>
+  </si>
+  <si>
+    <t>jennifer llanos </t>
   </si>
 </sst>
 </file>
@@ -1441,18 +1468,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1467,9 +1488,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1478,7 +1498,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1808,6 +1837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2943,11 +2973,11 @@
       <c r="E49" t="s">
         <v>294</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>77</v>
+      <c r="F49" t="s">
+        <v>466</v>
+      </c>
+      <c r="G49" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -2966,11 +2996,11 @@
       <c r="E50" t="s">
         <v>295</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>77</v>
+      <c r="F50" t="s">
+        <v>466</v>
+      </c>
+      <c r="G50" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -2989,11 +3019,11 @@
       <c r="E51" t="s">
         <v>193</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>77</v>
+      <c r="F51" t="s">
+        <v>466</v>
+      </c>
+      <c r="G51" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -3265,10 +3295,10 @@
       <c r="E63" t="s">
         <v>304</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="F63" t="s">
         <v>462</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" t="s">
         <v>461</v>
       </c>
     </row>
@@ -3288,10 +3318,10 @@
       <c r="E64" t="s">
         <v>222</v>
       </c>
-      <c r="F64" s="3" t="s">
+      <c r="F64" t="s">
         <v>462</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" t="s">
         <v>461</v>
       </c>
     </row>
@@ -3311,10 +3341,10 @@
       <c r="E65" t="s">
         <v>225</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" t="s">
         <v>462</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" t="s">
         <v>461</v>
       </c>
     </row>
@@ -3334,11 +3364,11 @@
       <c r="E66" t="s">
         <v>305</v>
       </c>
-      <c r="F66" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>77</v>
+      <c r="F66" t="s">
+        <v>425</v>
+      </c>
+      <c r="G66" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -3449,11 +3479,11 @@
       <c r="E71" t="s">
         <v>239</v>
       </c>
-      <c r="F71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>77</v>
+      <c r="F71" t="s">
+        <v>447</v>
+      </c>
+      <c r="G71" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -3472,11 +3502,11 @@
       <c r="E72" t="s">
         <v>308</v>
       </c>
-      <c r="F72" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>77</v>
+      <c r="F72" t="s">
+        <v>447</v>
+      </c>
+      <c r="G72" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -3495,11 +3525,11 @@
       <c r="E73" t="s">
         <v>244</v>
       </c>
-      <c r="F73" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>77</v>
+      <c r="F73" t="s">
+        <v>470</v>
+      </c>
+      <c r="G73" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -3656,11 +3686,11 @@
       <c r="E80" t="s">
         <v>261</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>77</v>
+      <c r="F80" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -3679,11 +3709,11 @@
       <c r="E81" t="s">
         <v>264</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G81" s="1" t="s">
-        <v>77</v>
+      <c r="F81" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -3702,11 +3732,11 @@
       <c r="E82" t="s">
         <v>457</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>77</v>
+      <c r="F82" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -3725,11 +3755,11 @@
       <c r="E83" t="s">
         <v>456</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>77</v>
+      <c r="F83" t="s">
+        <v>467</v>
+      </c>
+      <c r="G83" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -3748,11 +3778,11 @@
       <c r="E84" t="s">
         <v>270</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>77</v>
+      <c r="F84" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -3817,11 +3847,11 @@
       <c r="E87" t="s">
         <v>278</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G87" s="1" t="s">
-        <v>77</v>
+      <c r="F87" t="s">
+        <v>464</v>
+      </c>
+      <c r="G87" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -3969,16 +3999,16 @@
       <c r="B94" t="s">
         <v>316</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D94" s="2" t="s">
+      <c r="D94" s="1" t="s">
         <v>318</v>
       </c>
       <c r="E94" t="s">
         <v>319</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="F94" s="1" t="s">
         <v>320</v>
       </c>
       <c r="G94" t="s">
@@ -3992,16 +4022,16 @@
       <c r="B95" t="s">
         <v>316</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C95" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D95" s="2" t="s">
+      <c r="D95" s="1" t="s">
         <v>323</v>
       </c>
       <c r="E95" t="s">
         <v>324</v>
       </c>
-      <c r="F95" s="2" t="s">
+      <c r="F95" s="1" t="s">
         <v>325</v>
       </c>
       <c r="G95" t="s">
@@ -4015,16 +4045,16 @@
       <c r="B96" t="s">
         <v>316</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="1" t="s">
         <v>328</v>
       </c>
       <c r="E96" t="s">
         <v>329</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="F96" s="1" t="s">
         <v>325</v>
       </c>
       <c r="G96" t="s">
@@ -4038,16 +4068,16 @@
       <c r="B97" t="s">
         <v>316</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="C97" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="1" t="s">
         <v>331</v>
       </c>
       <c r="E97" t="s">
         <v>332</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="F97" s="1" t="s">
         <v>325</v>
       </c>
       <c r="G97" t="s">
@@ -4061,16 +4091,16 @@
       <c r="B98" t="s">
         <v>316</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="D98" s="1" t="s">
         <v>334</v>
       </c>
       <c r="E98" t="s">
         <v>335</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F98" s="1" t="s">
         <v>336</v>
       </c>
       <c r="G98" t="s">
@@ -4084,16 +4114,16 @@
       <c r="B99" t="s">
         <v>316</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C99" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D99" s="2" t="s">
+      <c r="D99" s="1" t="s">
         <v>339</v>
       </c>
       <c r="E99" t="s">
         <v>340</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="F99" s="1" t="s">
         <v>341</v>
       </c>
       <c r="G99" t="s">
@@ -4559,6 +4589,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H151" xr:uid="{37800E50-6288-4855-903E-7D1C9ED078D0}">
+    <filterColumn colId="5">
+      <colorFilter dxfId="0"/>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="E94" r:id="rId1" display="mailto:miriam.sotov@redsalud.gob.cl" xr:uid="{CA864F29-52B2-43C7-A13E-76AEC8A49A4F}"/>
     <hyperlink ref="G94" r:id="rId2" display="mailto:sandra.felipe@redsalud.gob.cl" xr:uid="{E976CC02-5359-4441-A979-BD71659626F9}"/>
